--- a/Flash_Portfolio.xlsx
+++ b/Flash_Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TradinAgentClaudeV2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{740B6326-1023-4AD7-B02F-569F8BEA2BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DDADB0-EEEB-483D-A002-F4FFF3E0468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3630" yWindow="3630" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1437,8 +1437,8 @@
       <c r="G12" s="5">
         <v>8</v>
       </c>
-      <c r="H12" s="6" t="s">
-        <v>17</v>
+      <c r="H12" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>17</v>

--- a/Flash_Portfolio.xlsx
+++ b/Flash_Portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TradinAgentClaudeV2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71DDADB0-EEEB-483D-A002-F4FFF3E0468C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F19784E-2FB7-47A9-86DF-9D7F7375CB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3630" yWindow="3630" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="167">
   <si>
     <t>Symbol</t>
   </si>
@@ -531,9 +531,6 @@
   </si>
   <si>
     <t>TMPV</t>
-  </si>
-  <si>
-    <t>VALIANTCO</t>
   </si>
 </sst>
 </file>
@@ -1416,8 +1413,8 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>167</v>
+      <c r="A12" s="2">
+        <v>526775</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>60</v>
@@ -1437,8 +1434,8 @@
       <c r="G12" s="5">
         <v>8</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>77</v>
+      <c r="H12" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>17</v>

--- a/Flash_Portfolio.xlsx
+++ b/Flash_Portfolio.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TradinAgentClaudeV2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\flash\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F19784E-2FB7-47A9-86DF-9D7F7375CB46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483F2D4C-F8C4-488D-867A-70A2F358078C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Portfolio" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="171">
   <si>
     <t>Symbol</t>
   </si>
@@ -531,6 +531,18 @@
   </si>
   <si>
     <t>TMPV</t>
+  </si>
+  <si>
+    <t>POWERINDIA</t>
+  </si>
+  <si>
+    <t>Electrical Equipment</t>
+  </si>
+  <si>
+    <t>Power grid &amp; energy transition play; strong order backlog</t>
+  </si>
+  <si>
+    <t>Hitachi Energy India Ltd</t>
   </si>
 </sst>
 </file>
@@ -642,7 +654,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -665,11 +677,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -714,6 +737,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -978,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="14.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
@@ -1942,6 +1971,44 @@
       </c>
       <c r="L25" s="8" t="s">
         <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="B26" t="s">
+        <v>170</v>
+      </c>
+      <c r="C26" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" t="s">
+        <v>168</v>
+      </c>
+      <c r="E26" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="16">
+        <v>1</v>
+      </c>
+      <c r="G26" s="17">
+        <v>15</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="16">
+        <v>6</v>
+      </c>
+      <c r="K26" s="16">
+        <v>33159.160000000003</v>
+      </c>
+      <c r="L26" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
